--- a/workflows/daily-report-generate-flow/out/steps/01-异常检测/异常预警清单.xlsx
+++ b/workflows/daily-report-generate-flow/out/steps/01-异常检测/异常预警清单.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -514,22 +514,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周二</t>
+          <t>周三</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>营收环比</t>
+          <t>营收连续趋势</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>R1 绝对阈值</t>
+          <t>R3 连续趋势</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -539,17 +539,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>连续 4 天下滑</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>环比 ≤ -20%</t>
+          <t>连续 ≥ 3 天 且 累计 &gt; 10%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>营收 6247 元（前一日 8929 元）</t>
+          <t>2026-09-05 → 2026-09-09 累计 -23.1%</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -559,54 +559,54 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>-2.3%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周一</t>
+          <t>周六</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>营收环比</t>
+          <t>转化率连续趋势</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>R1 绝对阈值</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R3 连续趋势</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>连续 4 天下滑</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>环比 ≤ -20%</t>
+          <t>连续 ≥ 3 天 且 累计 &gt; 10%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>营收 8929 元（前一日 11621 元）</t>
+          <t>2026-09-08 → 2026-09-12 累计 -30.7%</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -616,54 +616,54 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-38.9%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周二</t>
+          <t>周日</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>营收离群</t>
+          <t>退款率</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>R2 离群（Z-score(2σ)）</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>6247元</t>
+          <t>7.90%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>|x-μ| &gt; 2σ</t>
+          <t>&gt; 5.0%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Z=-2.30（μ=9521.8，σ=1423.8）</t>
+          <t>退款 965 元 / 营收 12221 元</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -673,24 +673,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>+32.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>+7.2%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周三</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -703,14 +703,14 @@
           <t>R1 绝对阈值</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>6.79%</t>
+          <t>7.90%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>退款 624 元 / 营收 9184 元</t>
+          <t>退款 705 元 / 营收 8925 元</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -730,54 +730,54 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>+4.8%</t>
+          <t>-0.7%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>周三</t>
+          <t>周二</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>退款率离群</t>
+          <t>退款率</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>R2 离群（Z-score(2σ)）</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>6.79%</t>
+          <t>7.90%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>|x-μ| &gt; 2σ</t>
+          <t>&gt; 5.0%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Z=+3.62（μ=2.7，σ=1.1）</t>
+          <t>退款 705 元 / 营收 8928 元</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,29 +787,29 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+4.8%</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周一</t>
+          <t>周三</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>营收环比</t>
+          <t>退款率</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -817,24 +817,24 @@
           <t>R1 绝对阈值</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>7.89%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>环比 ≤ -20%</t>
+          <t>&gt; 5.0%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>营收 9352 元（前一日 12018 元）</t>
+          <t>退款 760 元 / 营收 9632 元</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -844,69 +844,1038 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>+2.3%</t>
+          <t>+5.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+4.7%</t>
+          <t>+9.8%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>退款率</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>7.89%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>&gt; 5.0%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>退款 720 元 / 营收 9121 元</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>确认异常</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>+1.8%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>营收环比</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-80.2%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>环比 ≤ -20%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>营收 2389 元（前一日 12063 元）</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>确认异常</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-74.1%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-80.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>营收同比</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>R4 季节性（同比优先）</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-25.0%</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>同比偏离 ≥ 20%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>去年同期 11922 元，本期 8942 元</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>确认异常</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>+3.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>营收环比</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-20.6%</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>环比 ≤ -20%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>营收 6895 元（前一日 8679 元）</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>确认异常</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-34.2%</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>-38.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>营收环比</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-21.1%</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>环比 ≤ -20%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>营收 8986 元（前一日 11396 元）</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>确认异常</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-2.3%</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>营收环比</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-25.5%</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>环比 ≤ -20%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>营收 11661 元（前一日 15643 元）</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>确认异常</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>+11.3%</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>+69.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>营收环比</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-27.0%</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>环比 ≤ -20%</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>营收 8925 元（前一日 12221 元）</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>确认异常</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-3.0%</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>转化率</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1.45%</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>&lt; 1.5%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>访客 9364，订单 136</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>确认异常</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>转化率离群</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>R2 离群（Z-score(2σ)）</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1.45%</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>|x-μ| &gt; 2σ</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Z=-2.01（μ=2.7，σ=0.6）</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>确认异常</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>周三</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>退款率连续趋势</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>R3 连续趋势</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>转化率</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>连续 4 天下滑</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>连续 ≥ 3 天 且 累计 &gt; 10%</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-09-11 → 2026-09-16 累计 -11.6%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>&lt; 1.5%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>访客 10090，订单 148</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>确认异常</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>+1.2%</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>+5.7%</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>+9.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>转化率</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>&lt; 1.5%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>访客 9733，订单 143</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>确认异常</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>+1.8%</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>营收离群</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>R2 离群（Z-score(2σ)）</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2389元</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>|x-μ| &gt; 2σ</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Z=-3.20（μ=9410.8，σ=2194.3）</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>确认异常</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-74.1%</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>-80.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>转化率</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0.80%</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>&lt; 1.5%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>访客 1880，订单 15 —— 单日 15 单 &lt; 20 单，失真，只报值不下结论</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>只报值不下结论</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-74.1%</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>-80.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>退款率</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>12.72%</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>&gt; 5.0%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>退款 304 元 / 营收 2389 元 —— 订单量不足，失真，只报值不下结论</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>只报值不下结论</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-74.1%</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>-80.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>转化率离群</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>R2 离群（Z-score(2σ)）</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0.80%</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>|x-μ| &gt; 2σ</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Z=-3.05（μ=2.7，σ=0.6） —— 当日仅 15 单，样本不足，只报值不下结论</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>只报值不下结论</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-74.1%</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>-80.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>退款率离群</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>R2 离群（Z-score(2σ)）</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>12.72%</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>|x-μ| &gt; 2σ</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Z=+3.28（μ=3.7，σ=2.7） —— 当日仅 15 单，样本不足，只报值不下结论</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>只报值不下结论</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-74.1%</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-80.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>营收离群</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>R2 离群（Z-score(2σ)）</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>拦截</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>15643元</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>|x-μ| &gt; 2σ</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Z=+2.84（μ=9410.8，σ=2194.3）</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>特殊期，需人工判断 —— 已拦截（促销日）</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>+55.8%</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>+80.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>营收环比</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>拦截</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-22.3%</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>环比 ≤ -20%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>营收 7089 元（前一日 9121 元）</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>特殊期，需人工判断 —— 已拦截（节假日）</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>-29.4%</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>-54.7%</t>
         </is>
       </c>
     </row>
@@ -921,7 +1890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1012,22 +1981,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8893</v>
+        <v>8653</v>
       </c>
       <c r="D2" t="n">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E2" t="n">
-        <v>4791</v>
+        <v>4620</v>
       </c>
       <c r="F2" t="n">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="G2" t="n">
-        <v>62.19</v>
+        <v>62.7</v>
       </c>
       <c r="H2" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="I2" t="n">
         <v>2.53</v>
@@ -1038,10 +2007,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>12.5</v>
+        <v>15.16</v>
       </c>
       <c r="L2" t="n">
-        <v>17.48</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="3">
@@ -1056,19 +2025,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8765</v>
+        <v>8870</v>
       </c>
       <c r="D3" t="n">
         <v>143</v>
       </c>
       <c r="E3" t="n">
-        <v>4802</v>
+        <v>4797</v>
       </c>
       <c r="F3" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G3" t="n">
-        <v>61.29</v>
+        <v>62.03</v>
       </c>
       <c r="H3" t="n">
         <v>2.98</v>
@@ -1077,13 +2046,13 @@
         <v>2.66</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.44</v>
+        <v>2.51</v>
       </c>
       <c r="K3" t="n">
-        <v>12.7</v>
+        <v>13.51</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.93</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="4">
@@ -1098,34 +2067,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8908</v>
+        <v>8272</v>
       </c>
       <c r="D4" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="E4" t="n">
-        <v>4517</v>
+        <v>4212</v>
       </c>
       <c r="F4" t="n">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="G4" t="n">
-        <v>65.02</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>3.03</v>
+        <v>2.99</v>
       </c>
       <c r="I4" t="n">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
       <c r="J4" t="n">
-        <v>1.63</v>
+        <v>-6.74</v>
       </c>
       <c r="K4" t="n">
-        <v>11.94</v>
+        <v>15.63</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.74</v>
+        <v>-7.69</v>
       </c>
     </row>
     <row r="5">
@@ -1140,34 +2109,34 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8793</v>
+        <v>8763</v>
       </c>
       <c r="D5" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E5" t="n">
-        <v>4774</v>
+        <v>4761</v>
       </c>
       <c r="F5" t="n">
-        <v>215</v>
+        <v>185</v>
       </c>
       <c r="G5" t="n">
-        <v>61.92</v>
+        <v>61.28</v>
       </c>
       <c r="H5" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.29</v>
+        <v>5.94</v>
       </c>
       <c r="K5" t="n">
-        <v>17.46</v>
+        <v>19.48</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.59</v>
+        <v>-12.75</v>
       </c>
     </row>
     <row r="6">
@@ -1182,34 +2151,34 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11077</v>
+        <v>11276</v>
       </c>
       <c r="D6" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E6" t="n">
-        <v>5988</v>
+        <v>5762</v>
       </c>
       <c r="F6" t="n">
-        <v>238</v>
+        <v>278</v>
       </c>
       <c r="G6" t="n">
-        <v>62.23</v>
+        <v>64.8</v>
       </c>
       <c r="H6" t="n">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="I6" t="n">
-        <v>2.15</v>
+        <v>2.47</v>
       </c>
       <c r="J6" t="n">
-        <v>25.98</v>
+        <v>28.68</v>
       </c>
       <c r="K6" t="n">
-        <v>13.13</v>
+        <v>14.86</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.83</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="7">
@@ -1224,34 +2193,34 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11621</v>
+        <v>10890</v>
       </c>
       <c r="D7" t="n">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="E7" t="n">
-        <v>6120</v>
+        <v>5792</v>
       </c>
       <c r="F7" t="n">
-        <v>308</v>
+        <v>249</v>
       </c>
       <c r="G7" t="n">
-        <v>62.82</v>
+        <v>62.95</v>
       </c>
       <c r="H7" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="I7" t="n">
-        <v>2.65</v>
+        <v>2.29</v>
       </c>
       <c r="J7" t="n">
-        <v>4.91</v>
+        <v>-3.42</v>
       </c>
       <c r="K7" t="n">
-        <v>12.85</v>
+        <v>18.46</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.68</v>
+        <v>18.06</v>
       </c>
     </row>
     <row r="8">
@@ -1266,34 +2235,34 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8929</v>
+        <v>9191</v>
       </c>
       <c r="D8" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E8" t="n">
-        <v>4645</v>
+        <v>4920</v>
       </c>
       <c r="F8" t="n">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="G8" t="n">
-        <v>64.7</v>
+        <v>62.95</v>
       </c>
       <c r="H8" t="n">
         <v>2.97</v>
       </c>
       <c r="I8" t="n">
-        <v>2.62</v>
+        <v>2.12</v>
       </c>
       <c r="J8" t="n">
-        <v>-23.16</v>
+        <v>-15.6</v>
       </c>
       <c r="K8" t="n">
-        <v>14.5</v>
+        <v>19.83</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.31</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="9">
@@ -1308,34 +2277,34 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6247</v>
+        <v>8942</v>
       </c>
       <c r="D9" t="n">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="E9" t="n">
-        <v>4478</v>
+        <v>4662</v>
       </c>
       <c r="F9" t="n">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="G9" t="n">
-        <v>60.65</v>
+        <v>63.87</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>3.33</v>
+        <v>2.68</v>
       </c>
       <c r="J9" t="n">
-        <v>-30.04</v>
+        <v>-2.71</v>
       </c>
       <c r="K9" t="n">
-        <v>14.29</v>
+        <v>-25</v>
       </c>
       <c r="L9" t="n">
-        <v>-17.48</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="10">
@@ -1350,34 +2319,34 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9184</v>
+        <v>8667</v>
       </c>
       <c r="D10" t="n">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E10" t="n">
-        <v>4923</v>
+        <v>4708</v>
       </c>
       <c r="F10" t="n">
-        <v>624</v>
+        <v>220</v>
       </c>
       <c r="G10" t="n">
-        <v>61.64</v>
+        <v>61.47</v>
       </c>
       <c r="H10" t="n">
-        <v>3.03</v>
+        <v>2.99</v>
       </c>
       <c r="I10" t="n">
-        <v>6.79</v>
+        <v>2.54</v>
       </c>
       <c r="J10" t="n">
-        <v>47.01</v>
+        <v>-3.08</v>
       </c>
       <c r="K10" t="n">
-        <v>11.85</v>
+        <v>15.78</v>
       </c>
       <c r="L10" t="n">
-        <v>1.71</v>
+        <v>-4.88</v>
       </c>
     </row>
     <row r="11">
@@ -1392,34 +2361,34 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9323</v>
+        <v>9264</v>
       </c>
       <c r="D11" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E11" t="n">
-        <v>5073</v>
+        <v>4938</v>
       </c>
       <c r="F11" t="n">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="G11" t="n">
-        <v>61.74</v>
+        <v>63.02</v>
       </c>
       <c r="H11" t="n">
         <v>2.98</v>
       </c>
       <c r="I11" t="n">
-        <v>2.19</v>
+        <v>2.43</v>
       </c>
       <c r="J11" t="n">
-        <v>1.51</v>
+        <v>6.89</v>
       </c>
       <c r="K11" t="n">
-        <v>15.46</v>
+        <v>15.67</v>
       </c>
       <c r="L11" t="n">
-        <v>0.74</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="12">
@@ -1434,34 +2403,34 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9077</v>
+        <v>8679</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="E12" t="n">
-        <v>9368</v>
+        <v>4524</v>
       </c>
       <c r="F12" t="n">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="G12" t="n">
-        <v>61.33</v>
+        <v>64.77</v>
       </c>
       <c r="H12" t="n">
-        <v>1.58</v>
+        <v>2.96</v>
       </c>
       <c r="I12" t="n">
-        <v>2.41</v>
+        <v>2.12</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.64</v>
+        <v>-6.31</v>
       </c>
       <c r="K12" t="n">
-        <v>16.43</v>
+        <v>13.84</v>
       </c>
       <c r="L12" t="n">
-        <v>1.59</v>
+        <v>-13.59</v>
       </c>
     </row>
     <row r="13">
@@ -1476,34 +2445,34 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11490</v>
+        <v>6895</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>124</v>
       </c>
       <c r="E13" t="n">
-        <v>11377</v>
+        <v>5957</v>
       </c>
       <c r="F13" t="n">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="G13" t="n">
-        <v>64.55</v>
+        <v>55.6</v>
       </c>
       <c r="H13" t="n">
-        <v>1.56</v>
+        <v>2.08</v>
       </c>
       <c r="I13" t="n">
-        <v>2.33</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>26.58</v>
+        <v>-20.56</v>
       </c>
       <c r="K13" t="n">
-        <v>13.86</v>
+        <v>15.8</v>
       </c>
       <c r="L13" t="n">
-        <v>1.83</v>
+        <v>-34.17</v>
       </c>
     </row>
     <row r="14">
@@ -1518,34 +2487,34 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12018</v>
+        <v>11396</v>
       </c>
       <c r="D14" t="n">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="E14" t="n">
-        <v>12243</v>
+        <v>5840</v>
       </c>
       <c r="F14" t="n">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="G14" t="n">
-        <v>61.95</v>
+        <v>65.12</v>
       </c>
       <c r="H14" t="n">
-        <v>1.58</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="J14" t="n">
-        <v>4.6</v>
+        <v>65.28</v>
       </c>
       <c r="K14" t="n">
-        <v>16.59</v>
+        <v>16.77</v>
       </c>
       <c r="L14" t="n">
-        <v>1.68</v>
+        <v>23.55</v>
       </c>
     </row>
     <row r="15">
@@ -1560,34 +2529,34 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9352</v>
+        <v>8986</v>
       </c>
       <c r="D15" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E15" t="n">
-        <v>5004</v>
+        <v>4873</v>
       </c>
       <c r="F15" t="n">
         <v>207</v>
       </c>
       <c r="G15" t="n">
-        <v>62.77</v>
+        <v>61.13</v>
       </c>
       <c r="H15" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="I15" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="J15" t="n">
-        <v>-22.18</v>
+        <v>-21.15</v>
       </c>
       <c r="K15" t="n">
-        <v>12.73</v>
+        <v>17.07</v>
       </c>
       <c r="L15" t="n">
-        <v>2.31</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="16">
@@ -1602,34 +2571,34 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9140</v>
+        <v>8773</v>
       </c>
       <c r="D16" t="n">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="E16" t="n">
-        <v>4834</v>
+        <v>4519</v>
       </c>
       <c r="F16" t="n">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="G16" t="n">
-        <v>62.6</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="I16" t="n">
-        <v>2.13</v>
+        <v>2.61</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.27</v>
+        <v>-2.37</v>
       </c>
       <c r="K16" t="n">
-        <v>14.8</v>
+        <v>16.04</v>
       </c>
       <c r="L16" t="n">
-        <v>1.22</v>
+        <v>-3.72</v>
       </c>
     </row>
     <row r="17">
@@ -1644,34 +2613,580 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9532</v>
+        <v>9186</v>
       </c>
       <c r="D17" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E17" t="n">
-        <v>5033</v>
+        <v>4944</v>
       </c>
       <c r="F17" t="n">
-        <v>248</v>
+        <v>207</v>
       </c>
       <c r="G17" t="n">
-        <v>63.13</v>
+        <v>62.49</v>
       </c>
       <c r="H17" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="K17" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>15643</v>
+      </c>
+      <c r="D18" t="n">
+        <v>227</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7047</v>
+      </c>
+      <c r="F18" t="n">
+        <v>247</v>
+      </c>
+      <c r="G18" t="n">
+        <v>68.91</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="J18" t="n">
+        <v>70.29000000000001</v>
+      </c>
+      <c r="K18" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="L18" t="n">
+        <v>55.75</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>11661</v>
+      </c>
+      <c r="D19" t="n">
+        <v>181</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5978</v>
+      </c>
+      <c r="F19" t="n">
+        <v>265</v>
+      </c>
+      <c r="G19" t="n">
+        <v>64.43000000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-25.46</v>
+      </c>
+      <c r="K19" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="L19" t="n">
+        <v>11.34</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>12221</v>
+      </c>
+      <c r="D20" t="n">
+        <v>194</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="n">
+        <v>965</v>
+      </c>
+      <c r="G20" t="n">
+        <v>62.99</v>
+      </c>
+      <c r="H20" t="n">
         <v>3</v>
       </c>
-      <c r="I17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="K17" t="n">
-        <v>11.63</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="I20" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K20" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="L20" t="n">
+        <v>32.49</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>8925</v>
+      </c>
+      <c r="D21" t="n">
+        <v>140</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4615</v>
+      </c>
+      <c r="F21" t="n">
+        <v>705</v>
+      </c>
+      <c r="G21" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="I21" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-26.97</v>
+      </c>
+      <c r="K21" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-2.95</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>8928</v>
+      </c>
+      <c r="D22" t="n">
+        <v>136</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9364</v>
+      </c>
+      <c r="F22" t="n">
+        <v>705</v>
+      </c>
+      <c r="G22" t="n">
+        <v>65.65000000000001</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I22" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K22" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>9632</v>
+      </c>
+      <c r="D23" t="n">
+        <v>148</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10090</v>
+      </c>
+      <c r="F23" t="n">
+        <v>760</v>
+      </c>
+      <c r="G23" t="n">
+        <v>65.08</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I23" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="J23" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="K23" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="L23" t="n">
+        <v>5.71</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>9121</v>
+      </c>
+      <c r="D24" t="n">
+        <v>143</v>
+      </c>
+      <c r="E24" t="n">
+        <v>9733</v>
+      </c>
+      <c r="F24" t="n">
+        <v>720</v>
+      </c>
+      <c r="G24" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I24" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-5.31</v>
+      </c>
+      <c r="K24" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>7089</v>
+      </c>
+      <c r="D25" t="n">
+        <v>120</v>
+      </c>
+      <c r="E25" t="n">
+        <v>5353</v>
+      </c>
+      <c r="F25" t="n">
+        <v>228</v>
+      </c>
+      <c r="G25" t="n">
+        <v>59.08</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-22.28</v>
+      </c>
+      <c r="K25" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-29.42</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>12063</v>
+      </c>
+      <c r="D26" t="n">
+        <v>186</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6223</v>
+      </c>
+      <c r="F26" t="n">
+        <v>261</v>
+      </c>
+      <c r="G26" t="n">
+        <v>64.84999999999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J26" t="n">
+        <v>70.17</v>
+      </c>
+      <c r="K26" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="L26" t="n">
+        <v>15.17</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2389</v>
+      </c>
+      <c r="D27" t="n">
+        <v>15</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1880</v>
+      </c>
+      <c r="F27" t="n">
+        <v>304</v>
+      </c>
+      <c r="G27" t="n">
+        <v>159.27</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I27" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-80.2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-74.09999999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>9684</v>
+      </c>
+      <c r="D28" t="n">
+        <v>157</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5240</v>
+      </c>
+      <c r="F28" t="n">
+        <v>214</v>
+      </c>
+      <c r="G28" t="n">
+        <v>61.68</v>
+      </c>
+      <c r="H28" t="n">
         <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="J28" t="n">
+        <v>305.36</v>
+      </c>
+      <c r="K28" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>9236</v>
+      </c>
+      <c r="D29" t="n">
+        <v>142</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4790</v>
+      </c>
+      <c r="F29" t="n">
+        <v>208</v>
+      </c>
+      <c r="G29" t="n">
+        <v>65.04000000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-4.63</v>
+      </c>
+      <c r="K29" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="L29" t="n">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>9618</v>
+      </c>
+      <c r="D30" t="n">
+        <v>154</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5156</v>
+      </c>
+      <c r="F30" t="n">
+        <v>251</v>
+      </c>
+      <c r="G30" t="n">
+        <v>62.45</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J30" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="K30" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="L30" t="n">
+        <v>5.55</v>
       </c>
     </row>
   </sheetData>
@@ -1685,7 +3200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1740,13 +3255,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8893</v>
+        <v>8653</v>
       </c>
       <c r="D2" t="n">
-        <v>7570</v>
+        <v>8940</v>
       </c>
       <c r="E2" t="n">
-        <v>17.48</v>
+        <v>-3.21</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1766,13 +3281,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8765</v>
+        <v>8870</v>
       </c>
       <c r="D3" t="n">
-        <v>9030</v>
+        <v>9112</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.93</v>
+        <v>-2.66</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1792,13 +3307,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8908</v>
+        <v>8272</v>
       </c>
       <c r="D4" t="n">
-        <v>9254</v>
+        <v>8961</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.74</v>
+        <v>-7.69</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1818,13 +3333,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8793</v>
+        <v>8763</v>
       </c>
       <c r="D5" t="n">
-        <v>8935</v>
+        <v>10044</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.59</v>
+        <v>-12.75</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1844,13 +3359,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11077</v>
+        <v>11276</v>
       </c>
       <c r="D6" t="n">
-        <v>11284</v>
+        <v>10474</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.83</v>
+        <v>7.66</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1870,13 +3385,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11621</v>
+        <v>10890</v>
       </c>
       <c r="D7" t="n">
-        <v>11820</v>
+        <v>9224</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.68</v>
+        <v>18.06</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1896,13 +3411,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8929</v>
+        <v>9191</v>
       </c>
       <c r="D8" t="n">
-        <v>9140</v>
+        <v>9196</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.31</v>
+        <v>-0.06</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1922,16 +3437,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6247</v>
+        <v>8942</v>
       </c>
       <c r="D9" t="n">
-        <v>7570</v>
+        <v>8940</v>
       </c>
       <c r="E9" t="n">
-        <v>-17.48</v>
+        <v>0.03</v>
       </c>
       <c r="F9" t="n">
-        <v>-29.75</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="10">
@@ -1946,16 +3461,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9184</v>
+        <v>8667</v>
       </c>
       <c r="D10" t="n">
-        <v>9030</v>
+        <v>9112</v>
       </c>
       <c r="E10" t="n">
-        <v>1.71</v>
+        <v>-4.88</v>
       </c>
       <c r="F10" t="n">
-        <v>4.78</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="11">
@@ -1970,16 +3485,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9323</v>
+        <v>9264</v>
       </c>
       <c r="D11" t="n">
-        <v>9254</v>
+        <v>8961</v>
       </c>
       <c r="E11" t="n">
-        <v>0.74</v>
+        <v>3.38</v>
       </c>
       <c r="F11" t="n">
-        <v>4.66</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="12">
@@ -1994,16 +3509,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9077</v>
+        <v>8679</v>
       </c>
       <c r="D12" t="n">
-        <v>8935</v>
+        <v>10044</v>
       </c>
       <c r="E12" t="n">
-        <v>1.59</v>
+        <v>-13.59</v>
       </c>
       <c r="F12" t="n">
-        <v>3.23</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="13">
@@ -2018,16 +3533,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11490</v>
+        <v>6895</v>
       </c>
       <c r="D13" t="n">
-        <v>11284</v>
+        <v>10474</v>
       </c>
       <c r="E13" t="n">
-        <v>1.83</v>
+        <v>-34.17</v>
       </c>
       <c r="F13" t="n">
-        <v>3.73</v>
+        <v>-38.85</v>
       </c>
     </row>
     <row r="14">
@@ -2042,16 +3557,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12018</v>
+        <v>11396</v>
       </c>
       <c r="D14" t="n">
-        <v>11820</v>
+        <v>9224</v>
       </c>
       <c r="E14" t="n">
-        <v>1.68</v>
+        <v>23.55</v>
       </c>
       <c r="F14" t="n">
-        <v>3.42</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="15">
@@ -2066,16 +3581,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9352</v>
+        <v>8986</v>
       </c>
       <c r="D15" t="n">
-        <v>9140</v>
+        <v>9196</v>
       </c>
       <c r="E15" t="n">
-        <v>2.31</v>
+        <v>-2.29</v>
       </c>
       <c r="F15" t="n">
-        <v>4.74</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="16">
@@ -2090,16 +3605,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9140</v>
+        <v>8773</v>
       </c>
       <c r="D16" t="n">
-        <v>9030</v>
+        <v>9112</v>
       </c>
       <c r="E16" t="n">
+        <v>-3.72</v>
+      </c>
+      <c r="F16" t="n">
         <v>1.22</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-0.48</v>
       </c>
     </row>
     <row r="17">
@@ -2114,16 +3629,328 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9532</v>
+        <v>9186</v>
       </c>
       <c r="D17" t="n">
-        <v>9254</v>
+        <v>8961</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>2.51</v>
       </c>
       <c r="F17" t="n">
-        <v>2.24</v>
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>15643</v>
+      </c>
+      <c r="D18" t="n">
+        <v>10044</v>
+      </c>
+      <c r="E18" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="F18" t="n">
+        <v>80.23999999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>11661</v>
+      </c>
+      <c r="D19" t="n">
+        <v>10474</v>
+      </c>
+      <c r="E19" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="F19" t="n">
+        <v>69.12</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>12221</v>
+      </c>
+      <c r="D20" t="n">
+        <v>9224</v>
+      </c>
+      <c r="E20" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="F20" t="n">
+        <v>7.24</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>8925</v>
+      </c>
+      <c r="D21" t="n">
+        <v>9196</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-2.95</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>8928</v>
+      </c>
+      <c r="D22" t="n">
+        <v>8940</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>9632</v>
+      </c>
+      <c r="D23" t="n">
+        <v>9112</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="F23" t="n">
+        <v>9.789999999999999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>9121</v>
+      </c>
+      <c r="D24" t="n">
+        <v>8961</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>7089</v>
+      </c>
+      <c r="D25" t="n">
+        <v>10044</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-29.42</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-54.68</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>周六</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>12063</v>
+      </c>
+      <c r="D26" t="n">
+        <v>10474</v>
+      </c>
+      <c r="E26" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>周日</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2389</v>
+      </c>
+      <c r="D27" t="n">
+        <v>9224</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-74.09999999999999</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-80.45</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>9684</v>
+      </c>
+      <c r="D28" t="n">
+        <v>9196</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>9236</v>
+      </c>
+      <c r="D29" t="n">
+        <v>8940</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>9618</v>
+      </c>
+      <c r="D30" t="n">
+        <v>9112</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-0.15</v>
       </c>
     </row>
   </sheetData>
@@ -2137,11 +3964,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
   </cols>
@@ -2171,16 +3998,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>数据质量</t>
+          <t>区间内缺失日期</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>无问题</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+          <t>1 天</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>未补零；环比在缺失处断开，不得跨缺口比较，否则会制造假跌</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>单日样本量不足</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-27（15 单）</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>转化率 0.8%、退款率 12.72%</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>订单 &lt; 20 单，转化率与退款率失真 —— 只报值不下结论</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2244,7 +4101,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -2268,7 +4125,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2292,7 +4149,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2304,7 +4161,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -2316,7 +4173,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -2328,7 +4185,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2340,7 +4197,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -2352,7 +4209,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>152349</t>
+          <t>272913</t>
         </is>
       </c>
     </row>
@@ -2364,7 +4221,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.71</t>
         </is>
       </c>
     </row>
@@ -2376,7 +4233,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>3.46</t>
         </is>
       </c>
     </row>
